--- a/04-ISO-Controls/Statement-of-Applicability.xlsx
+++ b/04-ISO-Controls/Statement-of-Applicability.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="239">
   <si>
-    <t xml:space="preserve">Simulated portfolio project - SecurePay Technologies Pvt. Ltd. is fictional. Not a certification claim. ISO/IEC 27001:2022 Annex A - all 93 controls. Status values for non-seeded controls are 'Planned' until assessed.</t>
+    <t xml:space="preserve">Simulated portfolio project - HawkPay Technologies Pvt. Ltd. is fictional. Not a certification claim. ISO/IEC 27001:2022 Annex A - all 93 controls. Status values for non-seeded controls are 'Planned' until assessed.</t>
   </si>
   <si>
     <t xml:space="preserve">Control</t>
